--- a/staff_forms/001_peer_evaluation--staff_forms.xlsx
+++ b/staff_forms/001_peer_evaluation--staff_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1194,8 +1194,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'communication_effectiveness',_'value':_'communication_effectiveness'}</t>
+          <t>communication_effectiveness</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'communication_effectiveness', 'value': 'Communication Effectiveness'}</t>
+          <t>communication effectiveness</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'collaboration_and_teamwork',_'value':_'collaboration_and_teamwork'}</t>
+          <t>collaboration_and_teamwork</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'collaboration_and_teamwork', 'value': 'Collaboration and Teamwork'}</t>
+          <t>collaboration and teamwork</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'problem_solving',_'value':_'problem_solving'}</t>
+          <t>problem_solving</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'problem_solving', 'value': 'Problem Solving'}</t>
+          <t>problem solving</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'creativity',_'value':_'creativity'}</t>
+          <t>creativity</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'creativity', 'value': 'Creativity'}</t>
+          <t>creativity</t>
         </is>
       </c>
     </row>
@@ -1291,12 +1291,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'innovation',_'value':_'innovation'}</t>
+          <t>innovation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'innovation', 'value': 'Innovation'}</t>
+          <t>innovation</t>
         </is>
       </c>
     </row>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'other', 'value': 'Other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'highly',_'value':_'highly'}</t>
+          <t>highly</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Highly', 'value': 'Highly'}</t>
+          <t>Highly</t>
         </is>
       </c>
     </row>
@@ -1342,12 +1342,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat',_'value':_'somewhat'}</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat', 'value': 'Somewhat'}</t>
+          <t>Somewhat</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_at_all',_'value':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not at all', 'value': 'Not at all'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'neutral',_'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Neutral', 'value': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1393,12 +1393,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_"don't_know",_'value':_"don't_know"}</t>
+          <t>don't_know</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': "Don't know", 'value': "Don't know"}</t>
+          <t>Don't know</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1410,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'submit'}</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Submit'}</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'reset'}</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Reset'}</t>
+          <t>Reset</t>
         </is>
       </c>
     </row>
